--- a/data/trans_orig/P23_1_2016_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco actual o pasado en 2016</t>
+          <t>Población según el consumo de tabaco actual o pasado en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>261403</t>
+          <t>259868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>311067</t>
+          <t>310598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,74%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>413321</t>
+          <t>412196</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>462351</t>
+          <t>461798</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>682140</t>
+          <t>685478</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>755330</t>
+          <t>758389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>118626</t>
+          <t>121279</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161813</t>
+          <t>161871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51404</t>
+          <t>51590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>82132</t>
+          <t>81805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180647</t>
+          <t>179132</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237431</t>
+          <t>232355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10878</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28099</t>
+          <t>28667</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5421</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>16421</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18211</t>
+          <t>18752</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39380</t>
+          <t>39478</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>209360</t>
+          <t>208943</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>256784</t>
+          <t>257851</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>137528</t>
+          <t>138674</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>181110</t>
+          <t>183101</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>359352</t>
+          <t>355404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>429553</t>
+          <t>424508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,53%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>436288</t>
+          <t>436338</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>503783</t>
+          <t>502146</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>634351</t>
+          <t>630060</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>699224</t>
+          <t>694235</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1091253</t>
+          <t>1091139</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1182223</t>
+          <t>1181692</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,3%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>191597</t>
+          <t>192244</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>243800</t>
+          <t>244964</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87075</t>
+          <t>88115</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125851</t>
+          <t>127425</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>290926</t>
+          <t>289015</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>357959</t>
+          <t>357194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16029</t>
+          <t>16015</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39140</t>
+          <t>38741</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14167</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33135</t>
+          <t>34312</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35034</t>
+          <t>35364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63311</t>
+          <t>63345</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>282068</t>
+          <t>278249</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>340714</t>
+          <t>341030</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>220199</t>
+          <t>222885</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>277245</t>
+          <t>278398</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>517710</t>
+          <t>516481</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>600301</t>
+          <t>599631</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,06%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>276947</t>
+          <t>278186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>332271</t>
+          <t>333790</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>444969</t>
+          <t>447812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>501863</t>
+          <t>502414</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>741502</t>
+          <t>739323</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>819999</t>
+          <t>822444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>122039</t>
+          <t>124707</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166596</t>
+          <t>168883</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>63641</t>
+          <t>64857</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100595</t>
+          <t>100184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>197628</t>
+          <t>200172</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>254949</t>
+          <t>255716</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10218</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26379</t>
+          <t>27792</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,47 +2110,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>17593</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10531</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>27627</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>1,35%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>17593</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10373</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>26733</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24612</t>
+          <t>24135</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47764</t>
+          <t>47005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>264773</t>
+          <t>263437</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>320035</t>
+          <t>319921</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181821</t>
+          <t>185307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>233577</t>
+          <t>235338</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>464231</t>
+          <t>463909</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>539712</t>
+          <t>541343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,12%</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>421299</t>
+          <t>421382</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>482921</t>
+          <t>484632</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>617540</t>
+          <t>618309</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>683434</t>
+          <t>683006</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1058463</t>
+          <t>1057775</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1147170</t>
+          <t>1151359</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,94%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>178507</t>
+          <t>176598</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>230191</t>
+          <t>228469</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>112121</t>
+          <t>111200</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>160230</t>
+          <t>158086</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>302977</t>
+          <t>303266</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>371689</t>
+          <t>374477</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>16795</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36523</t>
+          <t>35951</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36288</t>
+          <t>35604</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>37555</t>
+          <t>35212</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>65239</t>
+          <t>63213</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>228401</t>
+          <t>232503</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>284355</t>
+          <t>287648</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>209642</t>
+          <t>207140</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>261006</t>
+          <t>262001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>449779</t>
+          <t>451447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>525961</t>
+          <t>530724</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1451376</t>
+          <t>1449245</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1566437</t>
+          <t>1566820</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2165439</t>
+          <t>2176920</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2285150</t>
+          <t>2290098</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,51%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3656461</t>
+          <t>3658622</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3824575</t>
+          <t>3832103</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,29%</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>657162</t>
+          <t>657993</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>752570</t>
+          <t>752729</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>351632</t>
+          <t>351550</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>424406</t>
+          <t>427302</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1034000</t>
+          <t>1025856</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1154938</t>
+          <t>1154919</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>68270</t>
+          <t>69222</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>107230</t>
+          <t>105115</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56464</t>
+          <t>58049</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>92482</t>
+          <t>92247</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>134015</t>
+          <t>137785</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>185244</t>
+          <t>188696</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1033109</t>
+          <t>1033431</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1146631</t>
+          <t>1147404</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>796934</t>
+          <t>795476</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>900794</t>
+          <t>897454</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1858282</t>
+          <t>1860794</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2016034</t>
+          <t>2010892</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -3613,7 +3613,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco actual o pasado en 2023</t>
+          <t>Población según el consumo de tabaco actual o pasado en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>313591</t>
+          <t>318213</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>370987</t>
+          <t>372335</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>486158</t>
+          <t>482023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>522222</t>
+          <t>521258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>813730</t>
+          <t>812896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>880364</t>
+          <t>876200</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,88%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96904</t>
+          <t>98998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133572</t>
+          <t>134948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>39467</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60052</t>
+          <t>61049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142251</t>
+          <t>142116</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186371</t>
+          <t>185445</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2736</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>13987</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14015</t>
+          <t>13894</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10718</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25144</t>
+          <t>24223</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148649</t>
+          <t>148145</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>196437</t>
+          <t>197017</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>97866</t>
+          <t>97370</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131474</t>
+          <t>131318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>256118</t>
+          <t>257026</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>315029</t>
+          <t>313942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>305592</t>
+          <t>258407</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>710425</t>
+          <t>707117</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>669466</t>
+          <t>669092</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>719127</t>
+          <t>718464</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>823555</t>
+          <t>863320</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1422394</t>
+          <t>1420161</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,16%</t>
+          <t>66,06%</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>187668</t>
+          <t>186900</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>756146</t>
+          <t>831397</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70487</t>
+          <t>70309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98636</t>
+          <t>98682</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263588</t>
+          <t>265838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1024466</t>
+          <t>1015381</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,23%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38222</t>
+          <t>39474</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13493</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32153</t>
+          <t>34561</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>25687</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60187</t>
+          <t>64224</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>117624</t>
+          <t>100006</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>285398</t>
+          <t>287059</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138811</t>
+          <t>138472</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>180667</t>
+          <t>179902</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>268291</t>
+          <t>255308</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>437132</t>
+          <t>438626</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>329663</t>
+          <t>329883</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>391216</t>
+          <t>390952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>625684</t>
+          <t>626318</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>803123</t>
+          <t>817887</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>968200</t>
+          <t>965052</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1247523</t>
+          <t>1265357</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>122679</t>
+          <t>121139</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>168695</t>
+          <t>164211</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38522</t>
+          <t>37064</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>103313</t>
+          <t>102503</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145092</t>
+          <t>140102</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>259315</t>
+          <t>257652</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,73%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18242</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53821</t>
+          <t>59051</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31091</t>
+          <t>31254</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31478</t>
+          <t>31930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74898</t>
+          <t>76504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143190</t>
+          <t>143734</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198359</t>
+          <t>198429</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75009</t>
+          <t>67105</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>186061</t>
+          <t>184972</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>201767</t>
+          <t>189467</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>361454</t>
+          <t>363386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -5515,12 +5515,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>480822</t>
+          <t>481794</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>547619</t>
+          <t>549134</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>732004</t>
+          <t>732082</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>825115</t>
+          <t>830472</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5565,12 +5565,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1233961</t>
+          <t>1234805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1373999</t>
+          <t>1377194</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5600,12 +5600,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -5628,12 +5628,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170824</t>
+          <t>169963</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>218165</t>
+          <t>220390</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>103726</t>
+          <t>105027</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152637</t>
+          <t>153266</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>283166</t>
+          <t>285683</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>361147</t>
+          <t>357158</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5713,12 +5713,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -5741,12 +5741,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6792</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22399</t>
+          <t>23982</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5756,12 +5756,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12420</t>
+          <t>12146</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26809</t>
+          <t>26238</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>21840</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>43663</t>
+          <t>44704</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>177947</t>
+          <t>179386</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>232110</t>
+          <t>231063</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>138414</t>
+          <t>139000</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>199203</t>
+          <t>200269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>329196</t>
+          <t>332280</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>417926</t>
+          <t>416876</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,66%</t>
         </is>
       </c>
     </row>
@@ -6084,12 +6084,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1387859</t>
+          <t>1312916</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1932155</t>
+          <t>1930270</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6119,12 +6119,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2579319</t>
+          <t>2577228</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2873419</t>
+          <t>2847425</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>77,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3913971</t>
+          <t>3958696</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4690388</t>
+          <t>4683345</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6169,12 +6169,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,82%</t>
         </is>
       </c>
     </row>
@@ -6197,12 +6197,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>637003</t>
+          <t>641386</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1404653</t>
+          <t>1477012</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>42,72%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>261388</t>
+          <t>275698</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>376266</t>
+          <t>377059</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>946969</t>
+          <t>950224</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1975074</t>
+          <t>1829952</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -6310,12 +6310,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>51699</t>
+          <t>50492</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>104919</t>
+          <t>103371</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6325,12 +6325,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6345,12 +6345,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52177</t>
+          <t>51708</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86583</t>
+          <t>86365</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>113226</t>
+          <t>112110</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>174954</t>
+          <t>177347</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -6423,12 +6423,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>613920</t>
+          <t>600359</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>844674</t>
+          <t>838145</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6438,12 +6438,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6458,12 +6458,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>463952</t>
+          <t>483868</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>640144</t>
+          <t>643754</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1168029</t>
+          <t>1165792</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1454703</t>
+          <t>1459122</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_1_2016_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>259868</t>
+          <t>259987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>310598</t>
+          <t>311716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>46,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>412196</t>
+          <t>413139</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>461798</t>
+          <t>462682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>685478</t>
+          <t>686084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>758389</t>
+          <t>759758</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>50,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121279</t>
+          <t>119436</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>161871</t>
+          <t>161271</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>51590</t>
+          <t>50215</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81805</t>
+          <t>81834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>178625</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>232355</t>
+          <t>233278</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11127</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28667</t>
+          <t>27836</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16421</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>18735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39478</t>
+          <t>38552</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>208943</t>
+          <t>207011</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>257851</t>
+          <t>257902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>138674</t>
+          <t>136653</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183101</t>
+          <t>181646</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>355404</t>
+          <t>357640</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>424508</t>
+          <t>428547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,83%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>436338</t>
+          <t>434907</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>502146</t>
+          <t>499177</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>630060</t>
+          <t>633018</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>694235</t>
+          <t>698549</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>67,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1091139</t>
+          <t>1089314</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1181692</t>
+          <t>1186735</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,52%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>192244</t>
+          <t>193252</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>244964</t>
+          <t>245888</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88115</t>
+          <t>85352</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127425</t>
+          <t>124821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>289015</t>
+          <t>290347</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>357194</t>
+          <t>357304</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16015</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38741</t>
+          <t>39662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34312</t>
+          <t>35133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>34601</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>63345</t>
+          <t>63277</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>278249</t>
+          <t>279282</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>341030</t>
+          <t>337342</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>222885</t>
+          <t>220756</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>278398</t>
+          <t>277963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>516481</t>
+          <t>517004</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>599631</t>
+          <t>597826</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>278186</t>
+          <t>277791</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>333790</t>
+          <t>334902</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>447812</t>
+          <t>448180</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>502414</t>
+          <t>505475</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>739323</t>
+          <t>739411</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>822444</t>
+          <t>819702</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,17%</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>124707</t>
+          <t>123574</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>168883</t>
+          <t>168988</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>64857</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>100184</t>
+          <t>102516</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>200172</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>255716</t>
+          <t>257459</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,7%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10574</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27792</t>
+          <t>28044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10531</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27627</t>
+          <t>28596</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>24463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>48335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>263437</t>
+          <t>264237</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>319921</t>
+          <t>320076</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>185307</t>
+          <t>181840</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>235338</t>
+          <t>232314</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>463909</t>
+          <t>461530</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>541343</t>
+          <t>538691</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>421382</t>
+          <t>421838</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>484632</t>
+          <t>483436</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>618309</t>
+          <t>618389</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>683006</t>
+          <t>682906</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,31%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1057775</t>
+          <t>1059675</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1151359</t>
+          <t>1148694</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>176598</t>
+          <t>178806</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228469</t>
+          <t>230001</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>111200</t>
+          <t>113304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>158086</t>
+          <t>160213</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>303266</t>
+          <t>304940</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>374477</t>
+          <t>371420</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,76%</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16795</t>
+          <t>16268</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>35951</t>
+          <t>37467</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>14778</t>
+          <t>15600</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>35604</t>
+          <t>35763</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>35212</t>
+          <t>36747</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>63213</t>
+          <t>64789</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>232503</t>
+          <t>229539</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>287648</t>
+          <t>285442</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>207140</t>
+          <t>206872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>262001</t>
+          <t>262145</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>451447</t>
+          <t>446859</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>530724</t>
+          <t>524239</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,48%</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1449245</t>
+          <t>1454347</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1566820</t>
+          <t>1567651</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2176920</t>
+          <t>2166418</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2290098</t>
+          <t>2286805</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3658622</t>
+          <t>3660422</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3832103</t>
+          <t>3829403</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>657993</t>
+          <t>652164</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>752729</t>
+          <t>749469</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>351550</t>
+          <t>350920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>427302</t>
+          <t>428908</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1025856</t>
+          <t>1030338</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1154919</t>
+          <t>1155140</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>69222</t>
+          <t>69083</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>105115</t>
+          <t>105992</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>58049</t>
+          <t>58559</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>92247</t>
+          <t>93802</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3303,12 +3303,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>137785</t>
+          <t>134654</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>188696</t>
+          <t>186034</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3318,12 +3318,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1033431</t>
+          <t>1043197</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1147404</t>
+          <t>1147034</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>795476</t>
+          <t>796790</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>897454</t>
+          <t>904834</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1860794</t>
+          <t>1860282</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2010892</t>
+          <t>2013913</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -3803,32 +3803,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>341883</t>
+          <t>373889</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>318213</t>
+          <t>347470</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>372335</t>
+          <t>401039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3838,32 +3838,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>504044</t>
+          <t>550366</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>482023</t>
+          <t>531553</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>521258</t>
+          <t>570368</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3873,32 +3873,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>845928</t>
+          <t>924255</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>812896</t>
+          <t>889869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>876200</t>
+          <t>958602</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -3916,32 +3916,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>114512</t>
+          <t>122827</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98998</t>
+          <t>104524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134948</t>
+          <t>141248</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3951,32 +3951,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>49184</t>
+          <t>52856</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39467</t>
+          <t>42937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61049</t>
+          <t>65448</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3986,22 +3986,22 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>163696</t>
+          <t>175682</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142116</t>
+          <t>154336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>185445</t>
+          <t>199421</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -4029,32 +4029,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4064,22 +4064,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13894</t>
+          <t>15159</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4099,32 +4099,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>15946</t>
+          <t>18840</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>24223</t>
+          <t>27442</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -4142,32 +4142,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>171206</t>
+          <t>184028</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148145</t>
+          <t>160708</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>197017</t>
+          <t>211109</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4177,67 +4177,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>113388</t>
+          <t>119936</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>97370</t>
+          <t>103355</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131318</t>
+          <t>138659</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
+          <t>18,91%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>303964</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>276414</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>339065</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>21,36%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>19,43%</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>284594</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>257026</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>313942</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>21,72%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>19,62%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -4255,17 +4255,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4290,17 +4290,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4325,17 +4325,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1310164</t>
+          <t>1422741</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1310164</t>
+          <t>1422741</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1310164</t>
+          <t>1422741</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4372,32 +4372,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>552848</t>
+          <t>619541</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>258407</t>
+          <t>586547</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>707117</t>
+          <t>654678</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4407,32 +4407,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>694626</t>
+          <t>784958</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>669092</t>
+          <t>756060</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>718464</t>
+          <t>809999</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4442,32 +4442,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1247474</t>
+          <t>1404499</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>863320</t>
+          <t>1359419</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1420161</t>
+          <t>1447236</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>68,31%</t>
         </is>
       </c>
     </row>
@@ -4485,32 +4485,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>401011</t>
+          <t>173283</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>186900</t>
+          <t>149748</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>831397</t>
+          <t>195091</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4520,32 +4520,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>90061</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70309</t>
+          <t>75424</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98682</t>
+          <t>105892</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4555,32 +4555,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>484375</t>
+          <t>263345</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>265838</t>
+          <t>235953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1015381</t>
+          <t>294857</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -4598,32 +4598,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19989</t>
+          <t>20966</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7698</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39474</t>
+          <t>37910</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4633,67 +4633,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21465</t>
+          <t>23064</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14205</t>
+          <t>15562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34561</t>
+          <t>35763</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>44030</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>31326</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>62375</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>1,48%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>41453</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>25687</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>64224</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -4711,32 +4711,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>218013</t>
+          <t>233986</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100006</t>
+          <t>204379</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>287059</t>
+          <t>264766</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4746,32 +4746,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>158652</t>
+          <t>172755</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>138472</t>
+          <t>151555</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>179902</t>
+          <t>197905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4781,32 +4781,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>376665</t>
+          <t>406741</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>255308</t>
+          <t>368948</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>438626</t>
+          <t>445675</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -4824,17 +4824,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1191861</t>
+          <t>1047776</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1191861</t>
+          <t>1047776</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1191861</t>
+          <t>1047776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4859,17 +4859,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4894,17 +4894,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2149967</t>
+          <t>2118614</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2149967</t>
+          <t>2118614</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2149967</t>
+          <t>2118614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>361308</t>
+          <t>422128</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>329883</t>
+          <t>387813</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>390952</t>
+          <t>452431</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>702402</t>
+          <t>554727</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>626318</t>
+          <t>530635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>817887</t>
+          <t>581208</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1063709</t>
+          <t>976855</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>965052</t>
+          <t>933986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1265357</t>
+          <t>1022477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>63,34%</t>
         </is>
       </c>
     </row>
@@ -5054,32 +5054,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>142209</t>
+          <t>165441</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121139</t>
+          <t>143290</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>164211</t>
+          <t>190221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5089,32 +5089,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74851</t>
+          <t>83611</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37064</t>
+          <t>68411</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>102503</t>
+          <t>98778</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5124,32 +5124,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>217060</t>
+          <t>249051</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>140102</t>
+          <t>223859</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>257652</t>
+          <t>280317</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -5167,32 +5167,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32742</t>
+          <t>33178</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>18791</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59051</t>
+          <t>52254</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5202,32 +5202,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>22872</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>14715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31254</t>
+          <t>33320</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5237,32 +5237,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>51923</t>
+          <t>56050</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31930</t>
+          <t>40744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76504</t>
+          <t>77225</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -5280,32 +5280,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>168257</t>
+          <t>181148</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>143734</t>
+          <t>155265</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>198429</t>
+          <t>210606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5315,32 +5315,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>136932</t>
+          <t>151049</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67105</t>
+          <t>130363</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>184972</t>
+          <t>173343</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5350,32 +5350,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>305189</t>
+          <t>332197</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189467</t>
+          <t>300575</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>363386</t>
+          <t>368810</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -5393,17 +5393,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704516</t>
+          <t>801895</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5428,17 +5428,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5463,17 +5463,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1637881</t>
+          <t>1614154</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5510,32 +5510,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>514632</t>
+          <t>548647</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>481794</t>
+          <t>514219</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>549134</t>
+          <t>581885</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5545,32 +5545,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>767195</t>
+          <t>767572</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>732082</t>
+          <t>738554</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>830472</t>
+          <t>793324</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5580,32 +5580,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1281828</t>
+          <t>1316219</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1234805</t>
+          <t>1274877</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1377194</t>
+          <t>1357190</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>62,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -5623,32 +5623,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>194706</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>169963</t>
+          <t>178660</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>220390</t>
+          <t>227435</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5658,32 +5658,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>130637</t>
+          <t>140015</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>105027</t>
+          <t>121047</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>153266</t>
+          <t>160999</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5693,32 +5693,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>325343</t>
+          <t>341873</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>285683</t>
+          <t>309901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>357158</t>
+          <t>367854</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -5736,32 +5736,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12813</t>
+          <t>16661</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23982</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5771,32 +5771,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>18587</t>
+          <t>20841</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12146</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26238</t>
+          <t>30750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5806,32 +5806,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>31400</t>
+          <t>37502</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>21840</t>
+          <t>26657</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>44704</t>
+          <t>51291</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -5849,32 +5849,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>204680</t>
+          <t>222897</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>179386</t>
+          <t>195647</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>231063</t>
+          <t>253631</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5884,32 +5884,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>174607</t>
+          <t>186741</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>139000</t>
+          <t>167067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200269</t>
+          <t>211745</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5919,32 +5919,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>379286</t>
+          <t>409638</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>332280</t>
+          <t>376623</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>416876</t>
+          <t>444821</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -5962,17 +5962,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5997,17 +5997,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1091026</t>
+          <t>1115170</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1091026</t>
+          <t>1115170</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1091026</t>
+          <t>1115170</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6032,17 +6032,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2017858</t>
+          <t>2105232</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2017858</t>
+          <t>2105232</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2017858</t>
+          <t>2105232</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6079,32 +6079,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1770672</t>
+          <t>1964205</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1312916</t>
+          <t>1900089</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1930270</t>
+          <t>2028033</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>55,83%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6114,32 +6114,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2668268</t>
+          <t>2657623</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2577228</t>
+          <t>2611447</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2847425</t>
+          <t>2708244</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6149,32 +6149,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>4438940</t>
+          <t>4621828</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3958696</t>
+          <t>4541527</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>4683345</t>
+          <t>4710838</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>62,38%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>64,88%</t>
         </is>
       </c>
     </row>
@@ -6192,32 +6192,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>852438</t>
+          <t>663408</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>641386</t>
+          <t>618433</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1477012</t>
+          <t>708368</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6227,32 +6227,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>338037</t>
+          <t>366543</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>337336</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>377059</t>
+          <t>398317</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6262,32 +6262,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1190474</t>
+          <t>1029951</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>950224</t>
+          <t>976529</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1829952</t>
+          <t>1084078</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -6305,32 +6305,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>72354</t>
+          <t>79688</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50492</t>
+          <t>59573</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>103371</t>
+          <t>103793</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6340,32 +6340,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>68368</t>
+          <t>76733</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51708</t>
+          <t>62796</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>86365</t>
+          <t>96077</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6375,32 +6375,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>140722</t>
+          <t>156421</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>112110</t>
+          <t>130668</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>177347</t>
+          <t>187011</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -6418,32 +6418,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>762156</t>
+          <t>822060</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>600359</t>
+          <t>768890</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>838145</t>
+          <t>882148</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6453,32 +6453,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>583579</t>
+          <t>630481</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>483868</t>
+          <t>590213</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>643754</t>
+          <t>675429</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6488,32 +6488,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1345734</t>
+          <t>1452540</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1165792</t>
+          <t>1381395</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1459122</t>
+          <t>1529462</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -6531,17 +6531,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3457620</t>
+          <t>3529361</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6566,17 +6566,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3658251</t>
+          <t>3731380</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6601,17 +6601,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7115871</t>
+          <t>7260740</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
